--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -5248,8 +5248,8 @@
       <c r="F211" t="str">
         <v>РФ</v>
       </c>
-      <c r="G211" t="str">
-        <v/>
+      <c r="G211">
+        <v>47323</v>
       </c>
     </row>
     <row r="212">
@@ -5801,7 +5801,7 @@
         <v>РФ</v>
       </c>
       <c r="G235">
-        <v>46157</v>
+        <v>46521</v>
       </c>
     </row>
     <row r="236">
@@ -5939,7 +5939,7 @@
         <v>РФ</v>
       </c>
       <c r="G241">
-        <v>46204</v>
+        <v>46570</v>
       </c>
     </row>
     <row r="242">

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -19396,7 +19396,7 @@
         <v>РФ</v>
       </c>
       <c r="G826">
-        <v>46240</v>
+        <v>46624</v>
       </c>
     </row>
     <row r="827">
